--- a/public/excel/product/Giá thép hộp tôn mạ kẽm.xlsx
+++ b/public/excel/product/Giá thép hộp tôn mạ kẽm.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="64">
   <si>
     <t xml:space="preserve">Tên</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">Loại</t>
   </si>
   <si>
+    <t xml:space="preserve">Lô hàng</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thép hộp mạ kẽm 13 x 26 x 1.0 x 6m</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">Thép hình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISM221</t>
   </si>
   <si>
     <t xml:space="preserve">Thép hộp mạ kẽm 13 x 26 x 1.1 x 6m</t>
@@ -431,7 +437,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="37.85"/>
@@ -468,10 +474,13 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>6</v>
@@ -492,15 +501,18 @@
         <v>58.652</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>6</v>
@@ -521,15 +533,18 @@
         <v>64.092</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>6</v>
@@ -550,15 +565,18 @@
         <v>79.902</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>6</v>
@@ -579,15 +597,18 @@
         <v>40.971</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>6</v>
@@ -608,15 +629,18 @@
         <v>44.711</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>6</v>
@@ -637,15 +661,18 @@
         <v>55.252</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>6</v>
@@ -666,15 +693,18 @@
         <v>46.581</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>6</v>
@@ -695,15 +725,18 @@
         <v>51.682</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" s="6" t="n">
         <v>6</v>
@@ -724,15 +757,18 @@
         <v>64.262</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>6</v>
@@ -753,15 +789,18 @@
         <v>60.182</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>6</v>
@@ -782,15 +821,18 @@
         <v>65.792</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>6</v>
@@ -811,15 +853,18 @@
         <v>82.112</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>6</v>
@@ -840,15 +885,18 @@
         <v>92.313</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>6</v>
@@ -869,15 +917,18 @@
         <v>126.994</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>6</v>
@@ -898,15 +949,18 @@
         <v>160.485</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>6</v>
@@ -927,15 +981,18 @@
         <v>76.162</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>6</v>
@@ -956,15 +1013,18 @@
         <v>83.472</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>6</v>
@@ -985,15 +1045,18 @@
         <v>90.613</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>6</v>
@@ -1014,15 +1077,18 @@
         <v>116.283</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>6</v>
@@ -1043,15 +1109,18 @@
         <v>126.654</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>6</v>
@@ -1072,15 +1141,18 @@
         <v>203.666</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>6</v>
@@ -1101,15 +1173,18 @@
         <v>131.754</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>6</v>
@@ -1130,15 +1205,18 @@
         <v>224.917</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>6</v>
@@ -1159,15 +1237,18 @@
         <v>92.313</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>6</v>
@@ -1188,15 +1269,18 @@
         <v>100.983</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>6</v>
@@ -1217,15 +1301,18 @@
         <v>126.994</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>6</v>
@@ -1246,15 +1333,18 @@
         <v>247.017</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>6</v>
@@ -1275,15 +1365,18 @@
         <v>140.254</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>6</v>
@@ -1304,15 +1397,18 @@
         <v>153.855</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>6</v>
@@ -1333,15 +1429,18 @@
         <v>194.316</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>6</v>
@@ -1362,15 +1461,18 @@
         <v>272.858</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>6</v>
@@ -1391,15 +1493,18 @@
         <v>171.535</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>6</v>
@@ -1420,15 +1525,18 @@
         <v>261.468</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>6</v>
@@ -1449,15 +1557,18 @@
         <v>333.38</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>6</v>
@@ -1478,15 +1589,18 @@
         <v>368.911</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>6</v>
@@ -1507,15 +1621,18 @@
         <v>124.274</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>6</v>
@@ -1536,15 +1653,18 @@
         <v>136.344</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>6</v>
@@ -1565,15 +1685,18 @@
         <v>171.875</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B40" s="3" t="n">
         <v>6</v>
@@ -1594,15 +1717,18 @@
         <v>240.897</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>6</v>
@@ -1623,15 +1749,18 @@
         <v>171.535</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B42" s="3" t="n">
         <v>6</v>
@@ -1652,15 +1781,18 @@
         <v>216.586</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B43" s="3" t="n">
         <v>6</v>
@@ -1681,15 +1813,18 @@
         <v>275.748</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B44" s="3" t="n">
         <v>6</v>
@@ -1710,15 +1845,18 @@
         <v>304.989</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B45" s="3" t="n">
         <v>6</v>
@@ -1739,15 +1877,18 @@
         <v>328.62</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B46" s="3" t="n">
         <v>6</v>
@@ -1768,15 +1909,18 @@
         <v>351.57</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" s="3" t="n">
         <v>6</v>
@@ -1797,15 +1941,18 @@
         <v>391.182</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B48" s="3" t="n">
         <v>6</v>
@@ -1826,15 +1973,18 @@
         <v>464.794</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B49" s="3" t="n">
         <v>6</v>
@@ -1855,15 +2005,18 @@
         <v>261.468</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B50" s="3" t="n">
         <v>6</v>
@@ -1884,15 +2037,18 @@
         <v>333.38</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B51" s="3" t="n">
         <v>6</v>
@@ -1913,15 +2069,18 @@
         <v>368.911</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B52" s="3" t="n">
         <v>6</v>
@@ -1942,15 +2101,18 @@
         <v>423.822</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B53" s="3" t="n">
         <v>6</v>
@@ -1971,10 +2133,13 @@
         <v>506.44</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
